--- a/data/trans_dic/P40_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P40_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,41; 90,42</t>
+          <t>84,72; 90,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,12; 91,46</t>
+          <t>84,89; 91,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,84; 92,64</t>
+          <t>86,97; 92,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,95; 87,93</t>
+          <t>82,75; 88,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,82; 87,31</t>
+          <t>79,17; 87,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,38; 90,78</t>
+          <t>82,83; 90,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,69; 92,25</t>
+          <t>85,18; 92,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,49; 86,84</t>
+          <t>80,58; 86,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83,63; 88,43</t>
+          <t>83,64; 88,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,44; 90,57</t>
+          <t>85,48; 90,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87,18; 91,72</t>
+          <t>87,01; 91,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,43; 86,63</t>
+          <t>82,53; 86,8</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,47; 90,69</t>
+          <t>83,95; 90,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,23; 91,18</t>
+          <t>84,21; 91,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,71; 91,69</t>
+          <t>85,06; 91,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,84; 88,18</t>
+          <t>82,62; 88,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,4; 86,4</t>
+          <t>79,26; 86,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,13; 89,31</t>
+          <t>81,01; 89,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,54; 88,42</t>
+          <t>80,68; 88,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,99; 84,53</t>
+          <t>78,47; 84,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,83; 87,75</t>
+          <t>82,8; 88,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,29; 89,48</t>
+          <t>84,03; 89,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,24; 89,38</t>
+          <t>84,05; 89,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,12; 85,71</t>
+          <t>81,47; 85,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,57; 86,02</t>
+          <t>79,89; 85,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,24; 82,06</t>
+          <t>75,1; 81,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,32; 84,86</t>
+          <t>78,23; 85,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,42; 94,13</t>
+          <t>75,31; 82,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,37; 77,61</t>
+          <t>63,51; 77,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,72; 81,92</t>
+          <t>71,38; 82,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,4; 77,18</t>
+          <t>61,71; 77,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,44; 73,48</t>
+          <t>63,71; 74,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,15; 83,02</t>
+          <t>77,08; 82,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,04; 80,98</t>
+          <t>75,22; 80,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,44; 81,96</t>
+          <t>75,57; 82,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,47; 92,08</t>
+          <t>73,09; 78,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,23; 82,67</t>
+          <t>78,4; 82,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,62; 80,85</t>
+          <t>75,51; 80,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,77; 84,2</t>
+          <t>79,79; 84,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,22; 80,38</t>
+          <t>75,76; 80,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,16; 78,72</t>
+          <t>72,48; 78,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,63; 81,88</t>
+          <t>75,81; 81,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,92; 82,62</t>
+          <t>76,77; 82,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,8; 89,38</t>
+          <t>73,78; 78,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76,89; 80,56</t>
+          <t>76,99; 80,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,55; 80,35</t>
+          <t>76,4; 80,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,31; 82,9</t>
+          <t>79,11; 82,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,86; 86,15</t>
+          <t>75,73; 79,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,25; 83,03</t>
+          <t>74,55; 83,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,3; 86,55</t>
+          <t>80,06; 86,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,92; 80,48</t>
+          <t>73,73; 80,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,03; 78,59</t>
+          <t>73,99; 81,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,19; 72,63</t>
+          <t>64,89; 73,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,16; 68,16</t>
+          <t>60,8; 68,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,18; 71,46</t>
+          <t>64,22; 71,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,9; 64,01</t>
+          <t>59,48; 65,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70,02; 75,82</t>
+          <t>70,19; 76,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70,0; 75,0</t>
+          <t>69,66; 74,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,77; 74,91</t>
+          <t>69,97; 74,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,78; 68,68</t>
+          <t>66,36; 70,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,71; 97,59</t>
+          <t>92,98; 97,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,61; 98,83</t>
+          <t>93,15; 98,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,07; 96,44</t>
+          <t>91,25; 96,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86,18; 95,93</t>
+          <t>85,85; 95,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,94; 66,39</t>
+          <t>60,99; 66,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63,13; 68,84</t>
+          <t>62,83; 68,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,82</t>
+          <t>65,6; 71,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63,1; 69,06</t>
+          <t>64,18; 69,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67,63; 72,3</t>
+          <t>67,61; 72,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,18; 74,29</t>
+          <t>69,2; 74,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71,63; 76,67</t>
+          <t>71,03; 76,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,5; 75,09</t>
+          <t>69,72; 75,14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,73; 85,3</t>
+          <t>82,78; 85,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,59; 84,41</t>
+          <t>81,63; 84,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82,71; 85,35</t>
+          <t>82,7; 85,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,44; 85,96</t>
+          <t>80,19; 82,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,86; 73,05</t>
+          <t>69,96; 72,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,46; 74,6</t>
+          <t>71,59; 74,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,32; 76,44</t>
+          <t>73,23; 76,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68,34; 76,65</t>
+          <t>70,95; 73,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76,65; 78,69</t>
+          <t>76,63; 78,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76,99; 79,03</t>
+          <t>77,06; 79,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78,38; 80,32</t>
+          <t>78,43; 80,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,91; 79,96</t>
+          <t>75,87; 77,62</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431054</t>
+          <t>472582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>376599</t>
+          <t>408845</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>807654</t>
+          <t>881427</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>399895; 428375</t>
+          <t>401389; 430024</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>367168; 394524</t>
+          <t>366182; 395569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>371821; 396652</t>
+          <t>372374; 398024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>414026; 444248</t>
+          <t>455637; 487727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>241724; 267777</t>
+          <t>242800; 268919</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>257269; 283493</t>
+          <t>258665; 282659</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>291392; 317417</t>
+          <t>293075; 317446</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>364626; 388602</t>
+          <t>393550; 421319</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>652666; 690183</t>
+          <t>652776; 693375</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>635336; 673538</t>
+          <t>635637; 673806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673230; 708291</t>
+          <t>671951; 708610</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>785277; 825307</t>
+          <t>857509; 901858</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386088</t>
+          <t>414738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>311911</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>697999</t>
+          <t>760670</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>305552; 331978</t>
+          <t>307303; 332680</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350242; 379136</t>
+          <t>350145; 379024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>317921; 344130</t>
+          <t>319246; 344475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>370105; 398772</t>
+          <t>399211; 428640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>291529; 321295</t>
+          <t>294743; 322678</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>272563; 300063</t>
+          <t>272158; 300101</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>296613; 325660</t>
+          <t>297139; 326404</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>298356; 323388</t>
+          <t>332055; 358491</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>611234; 647494</t>
+          <t>611010; 650061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>633669; 672703</t>
+          <t>631717; 672191</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>626441; 664627</t>
+          <t>625032; 663899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>677203; 715502</t>
+          <t>738424; 778297</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>573620</t>
+          <t>371538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>114839</t>
+          <t>130667</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>688459</t>
+          <t>502205</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>430804; 465687</t>
+          <t>432516; 464236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>470771; 513443</t>
+          <t>469952; 513038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>408052; 442116</t>
+          <t>407588; 443435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>510715; 629061</t>
+          <t>355183; 388584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>106324; 130212</t>
+          <t>106558; 130315</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>182531; 211442</t>
+          <t>184245; 211773</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>102975; 127370</t>
+          <t>101844; 128358</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>104226; 122648</t>
+          <t>119462; 140362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>547104; 588781</t>
+          <t>546662; 587324</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>663249; 715756</t>
+          <t>664795; 715048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>517520; 562259</t>
+          <t>518440; 562531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>621931; 769036</t>
+          <t>481716; 520201</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805161</t>
+          <t>886242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>797758</t>
+          <t>657177</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1602917</t>
+          <t>1543419</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>968069; 1022951</t>
+          <t>970101; 1024639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>865160; 924977</t>
+          <t>863950; 922612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>908214; 958616</t>
+          <t>908340; 962086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>778404; 831767</t>
+          <t>857491; 914547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>515451; 562271</t>
+          <t>517711; 561988</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>575381; 622910</t>
+          <t>576677; 621734</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>630090; 676777</t>
+          <t>628896; 675901</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>741356; 874206</t>
+          <t>635420; 675820</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1500680; 1572236</t>
+          <t>1502643; 1573397</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1458226; 1530573</t>
+          <t>1455388; 1530009</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1552639; 1622872</t>
+          <t>1548675; 1621566</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1547114; 1734172</t>
+          <t>1509249; 1577057</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>356907</t>
+          <t>441389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>486172</t>
+          <t>519131</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>843079</t>
+          <t>960520</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>260289; 291052</t>
+          <t>261325; 292725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>403735; 435162</t>
+          <t>402484; 435981</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>454916; 495272</t>
+          <t>453732; 497697</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>337426; 373333</t>
+          <t>420264; 460138</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>370783; 413099</t>
+          <t>369059; 415656</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>464591; 517729</t>
+          <t>461820; 517999</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>471001; 524472</t>
+          <t>471313; 522944</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>352551; 538525</t>
+          <t>494187; 540513</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>643709; 697026</t>
+          <t>645267; 699787</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>883591; 946765</t>
+          <t>879301; 946165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>941359; 1010813</t>
+          <t>944141; 1007391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>707957; 904108</t>
+          <t>928184; 991068</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223185</t>
+          <t>217654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>503840</t>
+          <t>565791</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>727025</t>
+          <t>783445</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>276452; 291014</t>
+          <t>277259; 290966</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>241330; 254782</t>
+          <t>240151; 253877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>260652; 276019</t>
+          <t>261176; 276519</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>207265; 230724</t>
+          <t>203661; 225477</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>759896; 827812</t>
+          <t>760505; 828844</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>694624; 757443</t>
+          <t>691325; 757898</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>699221; 769067</t>
+          <t>702427; 767171</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>480400; 525798</t>
+          <t>541818; 589831</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1044957; 1117204</t>
+          <t>1044719; 1114600</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>939543; 1008923</t>
+          <t>939736; 1005823</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>972049; 1040438</t>
+          <t>963858; 1038050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>696283; 752329</t>
+          <t>754053; 812614</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2776014</t>
+          <t>2804142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2591118</t>
+          <t>2627542</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5367133</t>
+          <t>5431684</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2703184; 2787188</t>
+          <t>2704756; 2787069</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2755805; 2850953</t>
+          <t>2757181; 2853496</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2782801; 2871609</t>
+          <t>2782529; 2866974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2715627; 2901899</t>
+          <t>2760596; 2851235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2358820; 2466482</t>
+          <t>2362020; 2464436</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2520402; 2631078</t>
+          <t>2525034; 2634057</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2567127; 2676284</t>
+          <t>2564188; 2673116</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2444888; 2742371</t>
+          <t>2579363; 2671910</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5092654; 5228036</t>
+          <t>5090955; 5226297</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5315629; 5456900</t>
+          <t>5320280; 5463388</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5381621; 5514625</t>
+          <t>5384963; 5518078</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5209072; 5560525</t>
+          <t>5370259; 5493937</t>
         </is>
       </c>
     </row>
